--- a/forms/trg/Formulir_TRG_dynapop-maths.xlsx
+++ b/forms/trg/Formulir_TRG_dynapop-maths.xlsx
@@ -69,12 +69,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Daftar anggota tim belum terbaca dari situs. Mohon isi lengkap di lembar Anggota.</t>
+          <t>Data TRG ini relatif lengkap. Mohon periksa dan lengkapi mitra serta riset terbaik.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B16)</f>
+        <f>COUNTA(Anggota!B5:B17)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F16)</f>
+        <f>COUNTA(Anggota!F5:F17)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -911,215 +911,260 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Syamsuddin Toaha</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Dept. of Mathematics, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Mathematical Modelling</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-6819-3943</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>35489458600</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="11" t="n"/>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="11" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="11" t="n"/>
-      <c r="K16" s="11" t="n"/>
-      <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -1158,7 +1203,7 @@
           <t>Fakultas</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Mathematics &amp; Natural Science</t>
         </is>
@@ -1170,7 +1215,7 @@
           <t>Tema riset utama (pilih 1-3)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Matematika &amp; statistika</t>
         </is>
@@ -1182,10 +1227,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="n"/>
+      <c r="B6" s="12" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="11" t="n"/>
+      <c r="B7" s="12" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1193,7 +1238,7 @@
           <t>Kata kunci riset (5-10, pisahkan koma)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
+      <c r="B9" s="12" t="n"/>
       <c r="C9" s="13" t="n"/>
       <c r="D9" s="13" t="n"/>
       <c r="E9" s="13" t="n"/>
@@ -1206,7 +1251,7 @@
           <t>Deskripsi singkat TRG (maks. 3 kalimat)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n"/>
+      <c r="B10" s="12" t="n"/>
       <c r="C10" s="13" t="n"/>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="13" t="n"/>
@@ -1243,34 +1288,34 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
+      <c r="A14" s="12" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
+      <c r="A16" s="12" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1317,31 +1362,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="A22" s="12" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
+      <c r="A23" s="12" t="n"/>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="A24" s="12" t="n"/>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
